--- a/Horarios/Colectivos/322-Lujan/LaboralMarcosPaz.xlsx
+++ b/Horarios/Colectivos/322-Lujan/LaboralMarcosPaz.xlsx
@@ -160,7 +160,7 @@
     <tableColumn id="3" name="Luján"/>
     <tableColumn id="4" name="Plomer"/>
     <tableColumn id="5" name="Villars"/>
-    <tableColumn id="6" name="Las Heras"/>
+    <tableColumn id="6" name="General Las Heras"/>
     <tableColumn id="7" name="Marcos Paz"/>
   </tableColumns>
 </table>
@@ -495,7 +495,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Las Heras</t>
+          <t>General Las Heras</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -512,23 +512,29 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>135_104002-1</t>
+          <t>322 G · 07:59</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.3263888888888889</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.3423611111111111</v>
+        <v>0.3326388888888889</v>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.3618055555555555</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.3840277777777778</v>
+        <v>0.4173611111111111</v>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -539,23 +545,25 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>135_104003-1</t>
+          <t>322 H · 12:04</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5027777777777778</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.4930555555555556</v>
+        <v>0.5402777777777777</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.5090277777777777</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.5284722222222222</v>
+        <v>0.55625</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.5506944444444445</v>
+        <v>0.5993055555555555</v>
       </c>
     </row>
     <row r="4">
@@ -566,23 +574,29 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>135_104004-1</t>
+          <t>322 G · 17:34</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.6597222222222222</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.6756944444444445</v>
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.6951388888888889</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.7173611111111111</v>
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -591,12 +605,32 @@
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>322 H · 21:39</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>0.9020833333333333</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.9986111111111111</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -728,7 +762,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="1" t="n"/>
@@ -752,7 +786,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
@@ -777,7 +811,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/sube/cuandosubo</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-line-322-Buenos_Aires-1602-855399-579299-14</t>
         </is>
       </c>
       <c r="B20" s="1" t="n"/>
@@ -803,7 +837,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>https://cuandosubo.sube.gob.ar/onebusaway-api-webapp/api/where</t>
+          <t>https://moovitapp.com/index/es-419/transporte_p%C3%BAblico-time-322-Buenos_Aires-1602-855399-579299-6997958-0</t>
         </is>
       </c>
       <c r="B22" s="1" t="n"/>
@@ -829,7 +863,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>API</t>
+          <t>Estimado</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
